--- a/Timesheet.xlsx
+++ b/Timesheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\globo\Desktop\math-tutor-dc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A439AD-7ABD-4A10-A5B4-4CC4CCABEF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21544144-5498-4909-BA01-B25C9E86C8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="9030" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>JS</t>
   </si>
@@ -40,6 +40,12 @@
   </si>
   <si>
     <t>Created backend, moved deployment space to main repo, added Braden + tutor carousel, added feature to track which qr code was scanned</t>
+  </si>
+  <si>
+    <t>Made bigger data section</t>
+  </si>
+  <si>
+    <t>Fixed backend, ensuring all data works. Setting up financials and scheduling</t>
   </si>
 </sst>
 </file>
@@ -75,10 +81,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -359,18 +364,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -381,19 +386,38 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46078</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>45715</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>45716</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
